--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2021_arica_y_parinacota.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 15:43</t>
+    <t xml:space="preserve">2026-10-05 21:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
